--- a/21:22/PLteamsData21:22_with_tight_schedule.xlsx
+++ b/21:22/PLteamsData21:22_with_tight_schedule.xlsx
@@ -1173,7 +1173,7 @@
         <v>7</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1269,7 +1269,7 @@
         <v>5</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1333,7 +1333,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1461,7 +1461,7 @@
         <v>5</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1493,7 +1493,7 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1621,7 +1621,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1717,7 +1717,7 @@
         <v>6</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1813,7 +1813,7 @@
         <v>6</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1877,7 +1877,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2005,7 +2005,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2037,7 +2037,7 @@
         <v>5</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2101,7 +2101,7 @@
         <v>5</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2428,7 +2428,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -2524,7 +2524,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2652,7 +2652,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2748,7 +2748,7 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2876,7 +2876,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -3100,7 +3100,7 @@
         <v>5</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -3196,7 +3196,7 @@
         <v>6</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -3388,7 +3388,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -3651,7 +3651,7 @@
         <v>7</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3715,7 +3715,7 @@
         <v>6</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3811,7 +3811,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3907,7 +3907,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4067,7 +4067,7 @@
         <v>5</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4099,7 +4099,7 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4131,7 +4131,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4195,7 +4195,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4227,7 +4227,7 @@
         <v>5</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4291,7 +4291,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4323,7 +4323,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4387,7 +4387,7 @@
         <v>6</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4515,7 +4515,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -4611,7 +4611,7 @@
         <v>7</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -4643,7 +4643,7 @@
         <v>5</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -4906,7 +4906,7 @@
         <v>6</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4970,7 +4970,7 @@
         <v>7</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -5066,7 +5066,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5098,7 +5098,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5322,7 +5322,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -5450,7 +5450,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -5514,7 +5514,7 @@
         <v>6</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -5546,7 +5546,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -5610,7 +5610,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -5642,7 +5642,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -5738,7 +5738,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -5834,7 +5834,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -5898,7 +5898,7 @@
         <v>5</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -5930,7 +5930,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -6257,7 +6257,7 @@
         <v>6</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6385,7 +6385,7 @@
         <v>5</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6417,7 +6417,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6481,7 +6481,7 @@
         <v>6</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6545,7 +6545,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6577,7 +6577,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -6673,7 +6673,7 @@
         <v>5</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6737,7 +6737,7 @@
         <v>5</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -6865,7 +6865,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -6961,7 +6961,7 @@
         <v>6</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -7153,7 +7153,7 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -7384,7 +7384,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7448,7 +7448,7 @@
         <v>7</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -7512,7 +7512,7 @@
         <v>5</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -7544,7 +7544,7 @@
         <v>6</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -7576,7 +7576,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -7608,7 +7608,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -7640,7 +7640,7 @@
         <v>5</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -7768,7 +7768,7 @@
         <v>5</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -7896,7 +7896,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7992,7 +7992,7 @@
         <v>6</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -8056,7 +8056,7 @@
         <v>6</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -8088,7 +8088,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -8152,7 +8152,7 @@
         <v>6</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -8280,7 +8280,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -8671,7 +8671,7 @@
         <v>5</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -8831,7 +8831,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -8863,7 +8863,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -8927,7 +8927,7 @@
         <v>5</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -9055,7 +9055,7 @@
         <v>6</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -9087,7 +9087,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -9119,7 +9119,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -9247,7 +9247,7 @@
         <v>7</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -9311,7 +9311,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -9343,7 +9343,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -9407,7 +9407,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -9439,7 +9439,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -9535,7 +9535,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -9599,7 +9599,7 @@
         <v>5</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -9631,7 +9631,7 @@
         <v>6</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -9926,7 +9926,7 @@
         <v>6</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -9990,7 +9990,7 @@
         <v>7</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -10086,7 +10086,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -10118,7 +10118,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -10182,7 +10182,7 @@
         <v>5</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -10278,7 +10278,7 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -10310,7 +10310,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -10342,7 +10342,7 @@
         <v>5</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -10406,7 +10406,7 @@
         <v>6</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -10438,7 +10438,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -10502,7 +10502,7 @@
         <v>5</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -10598,7 +10598,7 @@
         <v>6</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -10662,7 +10662,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -10790,7 +10790,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -10886,7 +10886,7 @@
         <v>7</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -11341,7 +11341,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -11469,7 +11469,7 @@
         <v>5</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -11597,7 +11597,7 @@
         <v>6</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -11629,7 +11629,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -11725,7 +11725,7 @@
         <v>6</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -11757,7 +11757,7 @@
         <v>5</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -11821,7 +11821,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -11885,7 +11885,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -11917,7 +11917,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -12013,7 +12013,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -12205,7 +12205,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -12436,7 +12436,7 @@
         <v>5</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -12500,7 +12500,7 @@
         <v>7</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -12532,7 +12532,7 @@
         <v>6</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -12628,7 +12628,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -12852,7 +12852,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -12884,7 +12884,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -12916,7 +12916,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -12948,7 +12948,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -12980,7 +12980,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -13076,7 +13076,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -13140,7 +13140,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -13236,7 +13236,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -13268,7 +13268,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -13460,7 +13460,7 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -13723,7 +13723,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -13787,7 +13787,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -13851,7 +13851,7 @@
         <v>5</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -13883,7 +13883,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -13947,7 +13947,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -14011,7 +14011,7 @@
         <v>7</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -14075,7 +14075,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -14107,7 +14107,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -14139,7 +14139,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -14171,7 +14171,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -14203,7 +14203,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -14235,7 +14235,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -14267,7 +14267,7 @@
         <v>7</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -14363,7 +14363,7 @@
         <v>5</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -14459,7 +14459,7 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -14946,7 +14946,7 @@
         <v>6</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -15106,7 +15106,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -15138,7 +15138,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -15170,7 +15170,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -15202,7 +15202,7 @@
         <v>5</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -15266,7 +15266,7 @@
         <v>6</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -15330,7 +15330,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -15394,7 +15394,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -15426,7 +15426,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -15490,7 +15490,7 @@
         <v>5</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -15618,7 +15618,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -15650,7 +15650,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -15714,7 +15714,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -15746,7 +15746,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -15842,7 +15842,7 @@
         <v>7</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -15938,7 +15938,7 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -16201,7 +16201,7 @@
         <v>6</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -16329,7 +16329,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -16425,7 +16425,7 @@
         <v>6</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -16457,7 +16457,7 @@
         <v>5</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -16521,7 +16521,7 @@
         <v>5</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -16585,7 +16585,7 @@
         <v>6</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -16649,7 +16649,7 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -16681,7 +16681,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -16777,7 +16777,7 @@
         <v>7</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -16873,7 +16873,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -16937,7 +16937,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -17033,7 +17033,7 @@
         <v>5</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -17097,7 +17097,7 @@
         <v>7</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -17193,7 +17193,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -17424,7 +17424,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -17584,7 +17584,7 @@
         <v>6</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -17680,7 +17680,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -17712,7 +17712,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -17744,7 +17744,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -17776,7 +17776,7 @@
         <v>7</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -17904,7 +17904,7 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -17936,7 +17936,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -18000,7 +18000,7 @@
         <v>5</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -18064,7 +18064,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -18160,7 +18160,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -18224,7 +18224,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -18256,7 +18256,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -18448,7 +18448,7 @@
         <v>5</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -18743,7 +18743,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -18807,7 +18807,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -18935,7 +18935,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -18967,7 +18967,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -18999,7 +18999,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -19095,7 +19095,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -19127,7 +19127,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -19223,7 +19223,7 @@
         <v>6</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -19255,7 +19255,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -19319,7 +19319,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -19383,7 +19383,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -19415,7 +19415,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -19607,7 +19607,7 @@
         <v>7</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -19934,7 +19934,7 @@
         <v>7</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -19998,7 +19998,7 @@
         <v>7</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -20030,7 +20030,7 @@
         <v>6</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20094,7 +20094,7 @@
         <v>5</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20126,7 +20126,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -20286,7 +20286,7 @@
         <v>7</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -20414,7 +20414,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -20510,7 +20510,7 @@
         <v>6</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -20542,7 +20542,7 @@
         <v>7</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -20702,7 +20702,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -20798,7 +20798,7 @@
         <v>5</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -20830,7 +20830,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -21253,7 +21253,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -21317,7 +21317,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21413,7 +21413,7 @@
         <v>5</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -21509,7 +21509,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -21669,7 +21669,7 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -21861,7 +21861,7 @@
         <v>6</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -21957,7 +21957,7 @@
         <v>6</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -22149,7 +22149,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -22181,7 +22181,7 @@
         <v>5</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -22245,7 +22245,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -22476,7 +22476,7 @@
         <v>5</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -22540,7 +22540,7 @@
         <v>7</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -22636,7 +22636,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -22732,7 +22732,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -22828,7 +22828,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -22892,7 +22892,7 @@
         <v>5</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -22924,7 +22924,7 @@
         <v>5</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -22956,7 +22956,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -23116,7 +23116,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -23148,7 +23148,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -23212,7 +23212,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -23340,7 +23340,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -23404,7 +23404,7 @@
         <v>5</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -23436,7 +23436,7 @@
         <v>7</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -23731,7 +23731,7 @@
         <v>5</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -23859,7 +23859,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -23891,7 +23891,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -23955,7 +23955,7 @@
         <v>6</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -24179,7 +24179,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -24211,7 +24211,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -24403,7 +24403,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -24435,7 +24435,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -24499,7 +24499,7 @@
         <v>5</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -24531,7 +24531,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -24595,7 +24595,7 @@
         <v>6</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -24659,7 +24659,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -24723,7 +24723,7 @@
         <v>5</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -24755,7 +24755,7 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -24986,7 +24986,7 @@
         <v>6</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -25242,7 +25242,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -25274,7 +25274,7 @@
         <v>5</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -25338,7 +25338,7 @@
         <v>5</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -25402,7 +25402,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -25466,7 +25466,7 @@
         <v>5</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -25594,7 +25594,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -25658,7 +25658,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -25754,7 +25754,7 @@
         <v>5</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -25882,7 +25882,7 @@
         <v>6</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -25946,7 +25946,7 @@
         <v>5</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -25978,7 +25978,7 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
